--- a/public/templates/examples/A-043-DataInventoryDataMap-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-043-DataInventoryDataMap-EXAMPLE-M.xlsx
@@ -256,7 +256,7 @@
     <t xml:space="preserve">NIST SP 800-53 Rev. 5: CM-8, MP-4, PM-5, RA-2, SC-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Indiana statutes and administrative code: IC 24-4.9 — Data Breach Notification; 240 IAC 5 — IDACS Security (for CJIS-bearing types)</t>
+    <t xml:space="preserve">Indiana statutes and administrative code: IC 24-4.9: Data Breach Notification; 240 IAC 5: IDACS Security (for CJIS-bearing types)</t>
   </si>
   <si>
     <t xml:space="preserve">CJIS Security Policy v5.9: §5.5, §5.10  (CJIS-regulated data in scope via IDACS)</t>
@@ -321,17 +321,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
       <family val="0"/>
     </font>
     <font>

--- a/public/templates/examples/A-043-DataInventoryDataMap-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-043-DataInventoryDataMap-EXAMPLE-M.xlsx
@@ -315,7 +315,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -562,19 +562,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>552240</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>552240</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="857250" cy="857250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -599,7 +594,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -722,12 +717,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-043-DataInventoryDataMap-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-043-DataInventoryDataMap-EXAMPLE-M.xlsx
@@ -5,12 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0"/>
   </bookViews>
   <sheets>
     <sheet name="Register" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -220,7 +223,7 @@
     <t xml:space="preserve">Per county records retention</t>
   </si>
   <si>
-    <t xml:space="preserve">Summary</t>
+    <t>Summary (as of 2026-06-11)</t>
   </si>
   <si>
     <t xml:space="preserve">Total data types</t>
@@ -308,8 +311,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -435,7 +439,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -485,6 +489,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1057,11 +1069,11 @@
       <c r="I12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>32</v>
+      <c r="J12" s="13">
+        <v>46086</v>
+      </c>
+      <c r="K12" s="13">
+        <v>46270</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1092,11 +1104,11 @@
       <c r="I13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>32</v>
+      <c r="J13" s="13">
+        <v>46086</v>
+      </c>
+      <c r="K13" s="13">
+        <v>46270</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1127,11 +1139,11 @@
       <c r="I14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>32</v>
+      <c r="J14" s="13">
+        <v>46086</v>
+      </c>
+      <c r="K14" s="13">
+        <v>46270</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1162,11 +1174,11 @@
       <c r="I15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>32</v>
+      <c r="J15" s="13">
+        <v>46086</v>
+      </c>
+      <c r="K15" s="13">
+        <v>46270</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1197,11 +1209,11 @@
       <c r="I16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>32</v>
+      <c r="J16" s="13">
+        <v>46086</v>
+      </c>
+      <c r="K16" s="13">
+        <v>46270</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1232,11 +1244,11 @@
       <c r="I17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>32</v>
+      <c r="J17" s="13">
+        <v>46086</v>
+      </c>
+      <c r="K17" s="13">
+        <v>46270</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1267,11 +1279,11 @@
       <c r="I18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>32</v>
+      <c r="J18" s="13">
+        <v>46086</v>
+      </c>
+      <c r="K18" s="13">
+        <v>46183</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1295,7 +1307,6 @@
       </c>
       <c r="C21" s="8" t="n">
         <f aca="false">COUNTA(A12:A18)</f>
-        <v>7</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1304,7 +1315,6 @@
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">COUNTIF(D12:D18,"*Internal*")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1313,7 +1323,6 @@
       </c>
       <c r="C23" s="8" t="n">
         <f aca="false">COUNTIF(D12:D18,"*Restricted*")</f>
-        <v>5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1322,7 +1331,6 @@
       </c>
       <c r="C24" s="8" t="n">
         <f aca="false">COUNTIF(D12:D18,"*Confidential*")</f>
-        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1331,7 +1339,6 @@
       </c>
       <c r="C25" s="8" t="n">
         <f aca="false">COUNTIF(D12:D18,"*CJIS*")</f>
-        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1339,8 +1346,7 @@
         <v>70</v>
       </c>
       <c r="C26" s="8" t="n">
-        <f aca="true">COUNTIF(K12:K18,"&lt;"&amp;TODAY())</f>
-        <v>0</v>
+        <f aca="true">COUNTIF(K12:K18,"&lt;"&amp;DATE(2026,6,11))</f>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1517,8 +1523,8 @@
       <c r="C42" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>86</v>
+      <c r="D42" s="14">
+        <v>46083</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1531,8 +1537,8 @@
       <c r="C43" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>86</v>
+      <c r="D43" s="14">
+        <v>46083</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1568,8 +1574,8 @@
       <c r="A47" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>86</v>
+      <c r="B47" s="14">
+        <v>46083</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>5</v>
@@ -1608,7 +1614,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
